--- a/data/TTC/最新版班表/TTC_TA.xlsx
+++ b/data/TTC/最新版班表/TTC_TA.xlsx
@@ -966,10 +966,10 @@
       </c>
       <c r="P7" s="1" t="inlineStr">
         <is>
-          <t>6:41
-CF2011
-14:41
-8:00</t>
+          <t>5:35
+CF1003
+13:37
+8:02</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1238,10 +1238,10 @@
       </c>
       <c r="X8" s="1" t="inlineStr">
         <is>
-          <t>16:30
+          <t>12:40
 DO2W
-STD6
-24:30
+CG1504
+20:40
 8:00</t>
         </is>
       </c>
@@ -1322,10 +1322,10 @@
       </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
-          <t>6:02
-CH0008
-14:20
-8:18</t>
+          <t>5:15
+CF0001
+13:15
+8:00</t>
         </is>
       </c>
       <c r="G9" s="1" t="inlineStr">
@@ -1774,9 +1774,9 @@
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>7:00
-CG1012
-15:00
+          <t>5:15
+CG0001
+13:15
 8:00</t>
         </is>
       </c>
@@ -2215,10 +2215,10 @@
       </c>
       <c r="M13" s="1" t="inlineStr">
         <is>
-          <t>6:41
-CG0011
-14:59
-8:18</t>
+          <t>5:44
+CG0006
+13:59
+8:15</t>
         </is>
       </c>
       <c r="N13" s="1" t="inlineStr">
@@ -2450,9 +2450,9 @@
       </c>
       <c r="P14" s="1" t="inlineStr">
         <is>
-          <t>12:59
-CH0506
-20:59
+          <t>10:20
+CH1019
+18:20
 8:00</t>
         </is>
       </c>
@@ -2464,46 +2464,46 @@
 9:49</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="R14" s="1" t="inlineStr">
+        <is>
+          <t>10:52
+CH0022
+19:52
+9:00</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="T14" s="1" t="inlineStr">
-        <is>
-          <t>16:20
-CH0525
-24:31
-8:11</t>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="U14" s="1" t="inlineStr">
         <is>
-          <t>15:40
-CF0522
-24:01
-8:21</t>
+          <t>5:44
+CF1006
+14:20
+8:36</t>
         </is>
       </c>
       <c r="V14" s="1" t="inlineStr">
         <is>
-          <t>16:08
-CG2523
-24:31
-8:23</t>
+          <t>5:15
+CG1001
+13:15
+8:00</t>
         </is>
       </c>
       <c r="W14" s="1" t="inlineStr">
         <is>
-          <t>16:31
-CH3523
-24:31
-8:00</t>
+          <t>5:35
+CF1003
+14:14
+8:39</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -2824,10 +2824,10 @@
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
-          <t>11:13
-CF0025
-21:04
-9:51</t>
+          <t>12:40
+CH1504
+20:40
+8:00</t>
         </is>
       </c>
       <c r="K16" s="1" t="inlineStr">
@@ -2885,12 +2885,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="S16" s="1" t="inlineStr">
-        <is>
-          <t>5:40
-CF0004
-13:56
-8:16</t>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="T16" s="1" t="inlineStr">
@@ -2917,9 +2914,12 @@
 9:25</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="W16" s="1" t="inlineStr">
+        <is>
+          <t>9:17
+CF0017
+17:17
+8:00</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>13:08
-CF0509
-21:14
-8:06</t>
+          <t>5:44
+CG0006
+13:59
+8:15</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr">
         <is>
-          <t>10:20
-CF1019
-18:20
+          <t>5:15
+CH0001
+13:15
 8:00</t>
         </is>
       </c>
@@ -3556,17 +3556,17 @@
       </c>
       <c r="Y19" s="1" t="inlineStr">
         <is>
-          <t>12:45
-CH1501
-20:45
-8:00</t>
+          <t>5:35
+CF1002
+14:00
+8:25</t>
         </is>
       </c>
       <c r="Z19" s="1" t="inlineStr">
         <is>
-          <t>12:37
-CH0503
-20:37
+          <t>5:15
+CF0001
+13:15
 8:00</t>
         </is>
       </c>
@@ -4102,10 +4102,10 @@
       </c>
       <c r="M22" s="1" t="inlineStr">
         <is>
-          <t>13:20
-CH0512
-21:59
-8:39</t>
+          <t>12:14
+CG0501
+20:14
+8:00</t>
         </is>
       </c>
       <c r="N22" s="1" t="inlineStr">
@@ -4157,18 +4157,18 @@
       </c>
       <c r="U22" s="1" t="inlineStr">
         <is>
-          <t>12:37
-CH0503
-20:37
+          <t>7:42
+CH0014
+15:42
 8:00</t>
         </is>
       </c>
       <c r="V22" s="1" t="inlineStr">
         <is>
-          <t>12:08
-CF2501
-20:14
-8:06</t>
+          <t>5:40
+CF2004
+13:40
+8:00</t>
         </is>
       </c>
       <c r="W22" s="1" t="inlineStr">
@@ -4883,10 +4883,10 @@
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>12:13
-CH1501
-20:14
-8:01</t>
+          <t>15:40
+CG0522
+24:01
+8:21</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4948,10 +4948,10 @@
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>10:56
-CG1022
-19:52
-8:56</t>
+          <t>11:13
+CG0023
+19:28
+8:15</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
@@ -4977,26 +4977,26 @@
       </c>
       <c r="R26" s="1" t="inlineStr">
         <is>
-          <t>6:31
-CF1011
-14:59
-8:28</t>
+          <t>15:52
+CF1525
+24:31
+8:39</t>
         </is>
       </c>
       <c r="S26" s="1" t="inlineStr">
         <is>
-          <t>5:50
-CF0007
-13:50
-8:00</t>
+          <t>15:40
+CH0522
+24:01
+8:21</t>
         </is>
       </c>
       <c r="T26" s="1" t="inlineStr">
         <is>
-          <t>12:14
-CF0501
-20:14
-8:00</t>
+          <t>15:40
+CH0522
+24:01
+8:21</t>
         </is>
       </c>
       <c r="U26" s="1" t="inlineStr">
@@ -5531,10 +5531,10 @@
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
-          <t>5:15
-CF0001
-13:15
-8:00</t>
+          <t>6:02
+CH0008
+14:20
+8:18</t>
         </is>
       </c>
       <c r="G29" s="1" t="inlineStr">
@@ -5569,9 +5569,9 @@
       </c>
       <c r="K29" s="1" t="inlineStr">
         <is>
-          <t>5:15
-CG0001
-13:15
+          <t>7:00
+CG1012
+15:00
 8:00</t>
         </is>
       </c>
@@ -5585,10 +5585,10 @@
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
-          <t>5:44
-CG0006
-13:59
-8:15</t>
+          <t>6:41
+CG0011
+14:59
+8:18</t>
         </is>
       </c>
       <c r="N29" s="1" t="inlineStr">
@@ -5606,10 +5606,10 @@
       </c>
       <c r="P29" s="1" t="inlineStr">
         <is>
-          <t>5:35
-CF1003
-13:37
-8:02</t>
+          <t>6:41
+CF2011
+14:41
+8:00</t>
         </is>
       </c>
       <c r="Q29" s="1" t="inlineStr">
@@ -6123,9 +6123,9 @@
       </c>
       <c r="AD31" s="1" t="inlineStr">
         <is>
-          <t>16:08
-CF0527
-24:08
+          <t>13:08
+CG0508
+21:08
 8:00</t>
         </is>
       </c>
@@ -6194,10 +6194,10 @@
       </c>
       <c r="J32" s="1" t="inlineStr">
         <is>
-          <t>12:40
-CH1504
-20:40
-8:00</t>
+          <t>11:13
+CF0025
+21:04
+9:51</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -6244,10 +6244,10 @@
       </c>
       <c r="Q32" s="1" t="inlineStr">
         <is>
-          <t>12:14
-CF3501
-20:14
-8:00</t>
+          <t>6:02
+CG1009
+14:31
+8:29</t>
         </is>
       </c>
       <c r="R32" s="1" t="inlineStr">
@@ -6258,14 +6258,17 @@
 8:00</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="S32" s="1" t="inlineStr">
+        <is>
+          <t>5:40
+CF0004
+13:56
+8:16</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>DO3X</t>
+          <t>DO1</t>
         </is>
       </c>
       <c r="U32" s="1" t="inlineStr">
@@ -6284,12 +6287,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="W32" s="1" t="inlineStr">
-        <is>
-          <t>9:17
-CF0017
-17:17
-8:00</t>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="X32" s="1" t="inlineStr">
@@ -7095,10 +7095,10 @@
       </c>
       <c r="S36" s="1" t="inlineStr">
         <is>
-          <t>6:41
-CG0011
-14:59
-8:18</t>
+          <t>8:13
+CG0015
+16:13
+8:00</t>
         </is>
       </c>
       <c r="T36" s="1" t="inlineStr">
@@ -7196,26 +7196,26 @@
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>10:52
-CH0022
-19:52
-9:00</t>
+          <t>5:44
+CF0006
+13:59
+8:15</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr">
         <is>
-          <t>13:20
-CF0512
-21:59
-8:39</t>
+          <t>6:02
+CF0008
+14:20
+8:18</t>
         </is>
       </c>
       <c r="F37" s="1" t="inlineStr">
         <is>
-          <t>10:52
-CF0022
-19:52
-9:00</t>
+          <t>5:35
+CH0002
+14:40
+9:05</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7300,18 +7300,18 @@
       </c>
       <c r="R37" s="1" t="inlineStr">
         <is>
-          <t>15:52
-CF1525
-24:31
+          <t>6:31
+CF1011
+14:59
+8:28</t>
+        </is>
+      </c>
+      <c r="S37" s="1" t="inlineStr">
+        <is>
+          <t>13:20
+CH0512
+21:59
 8:39</t>
-        </is>
-      </c>
-      <c r="S37" s="1" t="inlineStr">
-        <is>
-          <t>15:20
-CH0523
-24:31
-9:11</t>
         </is>
       </c>
       <c r="T37" s="1" t="inlineStr">
@@ -7411,33 +7411,33 @@
 8:21</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="E38" s="1" t="inlineStr">
-        <is>
-          <t>5:35
-CF0002
-14:40
-9:05</t>
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t>15:52
+CH1525
+24:31
+8:39</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>6:02
-CF0008
-14:20
-8:18</t>
+          <t>15:40
+CF0522
+24:01
+8:21</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>6:45
-CH0014
-15:45
-9:00</t>
+          <t>15:20
+CH1523
+24:31
+9:11</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -7547,9 +7547,12 @@
 8:00</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="X38" s="1" t="inlineStr">
+        <is>
+          <t>15:17
+CF0524
+24:31
+9:14</t>
         </is>
       </c>
       <c r="Y38" s="1" t="inlineStr">
@@ -7828,33 +7831,33 @@
 8:14</t>
         </is>
       </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>15:52
-CH1525
-24:31
-8:39</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="E40" s="1" t="inlineStr">
+        <is>
+          <t>5:35
+CF0002
+14:40
+9:05</t>
         </is>
       </c>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>15:40
-CF0522
-24:01
-8:21</t>
+          <t>6:02
+CF0008
+14:20
+8:18</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr">
         <is>
-          <t>15:20
-CH1523
-24:31
-9:11</t>
+          <t>6:45
+CH0014
+15:45
+9:00</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -8275,10 +8278,10 @@
       </c>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>12:59
+          <t>11:45
 DO2W
-CF0506
-20:59
+CF0027
+19:45
 8:00</t>
         </is>
       </c>
@@ -8406,10 +8409,10 @@
       </c>
       <c r="AA42" s="1" t="inlineStr">
         <is>
-          <t>5:40
-CG0004
-13:56
-8:16</t>
+          <t>6:41
+CG0011
+14:59
+8:18</t>
         </is>
       </c>
       <c r="AB42" s="1" t="inlineStr">
@@ -9125,10 +9128,10 @@
       </c>
       <c r="J46" s="1" t="inlineStr">
         <is>
-          <t>12:40
-CG1504
-20:40
-8:00</t>
+          <t>13:17
+CG0517
+23:03
+9:46</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -9159,10 +9162,10 @@
       </c>
       <c r="O46" s="1" t="inlineStr">
         <is>
-          <t>16:01
-CH1522
-24:01
-8:00</t>
+          <t>9:20
+CF0018
+18:45
+9:25</t>
         </is>
       </c>
       <c r="P46" s="1" t="inlineStr">
@@ -9435,11 +9438,8 @@
       </c>
       <c r="X47" s="1" t="inlineStr">
         <is>
-          <t>15:17
-DO2W
-CF0524
-24:31
-9:14</t>
+          <t>DO2W
+DO2</t>
         </is>
       </c>
       <c r="Y47" s="1" t="inlineStr">
@@ -9478,9 +9478,9 @@
       </c>
       <c r="AD47" s="1" t="inlineStr">
         <is>
-          <t>16:31
-CF3523
-24:31
+          <t>13:08
+CF0508
+21:08
 8:00</t>
         </is>
       </c>
@@ -9948,18 +9948,18 @@
       </c>
       <c r="G50" s="1" t="inlineStr">
         <is>
-          <t>9:57
-CH1022
-19:14
-9:17</t>
+          <t>6:02
+CG1008
+14:40
+8:38</t>
         </is>
       </c>
       <c r="H50" s="1" t="inlineStr">
         <is>
-          <t>8:33
-CF5903
-17:14
-8:41</t>
+          <t>6:02
+CG3008
+14:02
+8:00</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -10032,10 +10032,10 @@
       </c>
       <c r="S50" s="1" t="inlineStr">
         <is>
-          <t>8:13
-CG0015
-16:13
-8:00</t>
+          <t>6:41
+CG0011
+14:59
+8:18</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -10219,9 +10219,9 @@
       </c>
       <c r="P51" s="1" t="inlineStr">
         <is>
-          <t>9:17
-CH0017
-17:17
+          <t>6:02
+CG0009
+14:02
 8:00</t>
         </is>
       </c>
@@ -10708,12 +10708,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="Z53" s="1" t="inlineStr">
-        <is>
-          <t>12:14
-CG0501
-20:14
-8:00</t>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AA53" s="1" t="inlineStr">
@@ -10724,9 +10721,12 @@
 8:39</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AB53" s="1" t="inlineStr">
+        <is>
+          <t>11:45
+CF1026
+20:14
+8:29</t>
         </is>
       </c>
       <c r="AC53" s="1" t="inlineStr">
@@ -10920,10 +10920,10 @@
       </c>
       <c r="Z54" s="1" t="inlineStr">
         <is>
-          <t>13:20
-CF0512
-21:59
-8:39</t>
+          <t>15:20
+CH0523
+24:31
+9:11</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -11290,18 +11290,18 @@
       </c>
       <c r="S56" s="1" t="inlineStr">
         <is>
-          <t>15:20
-CF0523
-24:31
-9:11</t>
+          <t>5:50
+CF0007
+13:50
+8:00</t>
         </is>
       </c>
       <c r="T56" s="1" t="inlineStr">
         <is>
-          <t>15:40
-CH0522
-24:01
-8:21</t>
+          <t>12:14
+CF0501
+20:14
+8:00</t>
         </is>
       </c>
       <c r="U56" s="1" t="inlineStr">
@@ -11557,10 +11557,10 @@
       </c>
       <c r="Z57" s="1" t="inlineStr">
         <is>
-          <t>15:20
-CH0523
-24:31
-9:11</t>
+          <t>13:20
+CF0512
+21:59
+8:39</t>
         </is>
       </c>
       <c r="AA57" s="1" t="inlineStr">
@@ -12509,10 +12509,10 @@
       </c>
       <c r="J62" s="1" t="inlineStr">
         <is>
-          <t>13:17
-CG0517
-23:03
-9:46</t>
+          <t>12:40
+CG1504
+20:40
+8:00</t>
         </is>
       </c>
       <c r="K62" s="1" t="inlineStr">
@@ -13212,10 +13212,10 @@
       </c>
       <c r="U65" s="1" t="inlineStr">
         <is>
-          <t>16:31
-CF2525
-24:31
-8:00</t>
+          <t>15:40
+CG0522
+24:01
+8:21</t>
         </is>
       </c>
       <c r="V65" s="1" t="inlineStr">
@@ -13248,22 +13248,22 @@
 8:03</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Z65" s="1" t="inlineStr">
+        <is>
+          <t>12:14
+CG0501
+20:14
+8:00</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="AB65" s="1" t="inlineStr">
-        <is>
-          <t>11:45
-CF1026
-20:14
-8:29</t>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC65" s="1" t="inlineStr">
@@ -13610,12 +13610,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="R67" s="1" t="inlineStr">
-        <is>
-          <t>10:52
-CH0022
-19:52
-9:00</t>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="S67" s="1" t="inlineStr">
@@ -13626,41 +13623,44 @@
 8:39</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="T67" s="1" t="inlineStr">
+        <is>
+          <t>16:20
+CH0525
+24:31
+8:11</t>
         </is>
       </c>
       <c r="U67" s="1" t="inlineStr">
         <is>
-          <t>5:44
-CF1006
-14:20
-8:36</t>
+          <t>15:40
+CF0522
+24:01
+8:21</t>
         </is>
       </c>
       <c r="V67" s="1" t="inlineStr">
         <is>
-          <t>5:15
-CG1001
-13:15
-8:00</t>
+          <t>16:08
+CG2523
+24:31
+8:23</t>
         </is>
       </c>
       <c r="W67" s="1" t="inlineStr">
         <is>
-          <t>5:35
-CF1003
-14:14
-8:39</t>
+          <t>16:31
+CH3523
+24:31
+8:00</t>
         </is>
       </c>
       <c r="X67" s="1" t="inlineStr">
         <is>
-          <t>12:40
+          <t>16:30
 DO2W
-CG1504
-20:40
+STD6
+24:30
 8:00</t>
         </is>
       </c>
@@ -13911,9 +13911,9 @@
       </c>
       <c r="AD68" s="1" t="inlineStr">
         <is>
-          <t>13:08
-CF0508
-21:08
+          <t>16:31
+CF3523
+24:31
 8:00</t>
         </is>
       </c>
@@ -13936,26 +13936,26 @@
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t>5:44
-CF0006
-13:59
-8:15</t>
+          <t>10:52
+CH0022
+19:52
+9:00</t>
         </is>
       </c>
       <c r="E69" s="1" t="inlineStr">
         <is>
-          <t>6:02
-CF0008
-14:20
-8:18</t>
+          <t>13:20
+CF0512
+21:59
+8:39</t>
         </is>
       </c>
       <c r="F69" s="1" t="inlineStr">
         <is>
-          <t>5:35
-CH0002
-14:40
-9:05</t>
+          <t>10:52
+CF0022
+19:52
+9:00</t>
         </is>
       </c>
       <c r="G69" s="1" t="inlineStr">
@@ -14268,18 +14268,18 @@
       </c>
       <c r="U70" s="1" t="inlineStr">
         <is>
-          <t>7:42
-CH0014
-15:42
+          <t>12:37
+CH0503
+20:37
 8:00</t>
         </is>
       </c>
       <c r="V70" s="1" t="inlineStr">
         <is>
-          <t>5:40
-CF2004
-13:40
-8:00</t>
+          <t>12:08
+CF2501
+20:14
+8:06</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
@@ -14380,10 +14380,10 @@
       </c>
       <c r="G71" s="1" t="inlineStr">
         <is>
-          <t>15:17
-CG5902
-23:42
-8:25</t>
+          <t>12:25
+CG5901
+22:14
+9:49</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -14393,9 +14393,9 @@
       </c>
       <c r="I71" s="1" t="inlineStr">
         <is>
-          <t>11:45
-CF0027
-19:45
+          <t>12:59
+CF0506
+20:59
 8:00</t>
         </is>
       </c>
@@ -14435,17 +14435,17 @@
       </c>
       <c r="O71" s="1" t="inlineStr">
         <is>
-          <t>9:20
-CF0018
-18:45
-9:25</t>
+          <t>16:01
+CH1522
+24:01
+8:00</t>
         </is>
       </c>
       <c r="P71" s="1" t="inlineStr">
         <is>
-          <t>10:20
-CH1019
-18:20
+          <t>12:59
+CH0506
+20:59
 8:00</t>
         </is>
       </c>
@@ -14500,6 +14500,1706 @@
         </is>
       </c>
       <c r="X71" s="1" t="inlineStr">
+        <is>
+          <t>11:18
+DO2W
+CF0025
+21:14
+9:56</t>
+        </is>
+      </c>
+      <c r="Y71" s="1" t="inlineStr">
+        <is>
+          <t>10:17
+CG5904
+19:56
+9:39</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="AB71" s="1" t="inlineStr">
+        <is>
+          <t>6:41
+CF0011
+14:59
+8:18</t>
+        </is>
+      </c>
+      <c r="AC71" s="1" t="inlineStr">
+        <is>
+          <t>5:44
+CF0006
+13:59
+8:15</t>
+        </is>
+      </c>
+      <c r="AD71" s="1" t="inlineStr">
+        <is>
+          <t>6:02
+CF0009
+14:02
+8:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>A026933</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>蕭任求</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="inlineStr">
+        <is>
+          <t>13:56
+CF1518
+23:42
+9:46</t>
+        </is>
+      </c>
+      <c r="D72" s="1" t="inlineStr">
+        <is>
+          <t>15:52
+CF1525
+24:31
+8:39</t>
+        </is>
+      </c>
+      <c r="E72" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+PAY
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="F72" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+PAY
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="I72" s="1" t="inlineStr">
+        <is>
+          <t>16:31
+DO2W
+CH3523
+24:31
+8:00</t>
+        </is>
+      </c>
+      <c r="J72" s="1" t="inlineStr">
+        <is>
+          <t>13:56
+CG1518
+23:42
+9:46</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="L72" s="1" t="inlineStr">
+        <is>
+          <t>15:20
+CH0523
+24:31
+9:11</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="N72" s="1" t="inlineStr">
+        <is>
+          <t>12:37
+CG0503
+20:37
+8:00</t>
+        </is>
+      </c>
+      <c r="O72" s="1" t="inlineStr">
+        <is>
+          <t>12:40
+CG0504
+20:40
+8:00</t>
+        </is>
+      </c>
+      <c r="P72" s="1" t="inlineStr">
+        <is>
+          <t>12:59
+CG0506
+20:59
+8:00</t>
+        </is>
+      </c>
+      <c r="Q72" s="1" t="inlineStr">
+        <is>
+          <t>15:14
+CG0524
+24:31
+9:17</t>
+        </is>
+      </c>
+      <c r="R72" s="1" t="inlineStr">
+        <is>
+          <t>15:20
+CG0523
+24:31
+9:11</t>
+        </is>
+      </c>
+      <c r="S72" s="1" t="inlineStr">
+        <is>
+          <t>15:20
+CH0523
+24:31
+9:11</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="V72" s="1" t="inlineStr">
+        <is>
+          <t>5:35
+CF1002
+13:45
+8:10</t>
+        </is>
+      </c>
+      <c r="W72" s="1" t="inlineStr">
+        <is>
+          <t>6:02
+CH0009
+14:02
+8:00</t>
+        </is>
+      </c>
+      <c r="X72" s="1" t="inlineStr">
+        <is>
+          <t>5:35
+DO2W
+CG2003
+13:40
+8:05</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="Z72" s="1" t="inlineStr">
+        <is>
+          <t>5:35
+CF0002
+14:40
+9:05</t>
+        </is>
+      </c>
+      <c r="AA72" s="1" t="inlineStr">
+        <is>
+          <t>5:40
+CG0004
+13:56
+8:16</t>
+        </is>
+      </c>
+      <c r="AB72" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+OGT2
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="AC72" s="1" t="inlineStr">
+        <is>
+          <t>10:20
+CG0019
+19:14
+8:54</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>A026934</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>張雁婷</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="D73" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+PAY
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="E73" s="1" t="inlineStr">
+        <is>
+          <t>12:37
+CG0503
+20:37
+8:00</t>
+        </is>
+      </c>
+      <c r="F73" s="1" t="inlineStr">
+        <is>
+          <t>13:20
+CF0512
+21:59
+8:39</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="I73" s="1" t="inlineStr">
+        <is>
+          <t>16:08
+DO2W
+CG0527
+24:08
+8:00</t>
+        </is>
+      </c>
+      <c r="J73" s="1" t="inlineStr">
+        <is>
+          <t>14:13
+CH1513
+22:14
+8:01</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="M73" s="1" t="inlineStr">
+        <is>
+          <t>6:41
+CH0011
+14:59
+8:18</t>
+        </is>
+      </c>
+      <c r="N73" s="1" t="inlineStr">
+        <is>
+          <t>6:02
+CH1008
+14:40
+8:38</t>
+        </is>
+      </c>
+      <c r="O73" s="1" t="inlineStr">
+        <is>
+          <t>5:15
+CF1001
+13:15
+8:00</t>
+        </is>
+      </c>
+      <c r="P73" s="1" t="inlineStr">
+        <is>
+          <t>5:35
+CG1003
+13:37
+8:02</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="R73" s="1" t="inlineStr">
+        <is>
+          <t>6:02
+CF2008
+14:02
+8:00</t>
+        </is>
+      </c>
+      <c r="S73" s="1" t="inlineStr">
+        <is>
+          <t>6:41
+CH0011
+14:59
+8:18</t>
+        </is>
+      </c>
+      <c r="T73" s="1" t="inlineStr">
+        <is>
+          <t>5:44
+CF0006
+13:59
+8:15</t>
+        </is>
+      </c>
+      <c r="U73" s="1" t="inlineStr">
+        <is>
+          <t>5:35
+CF0003
+13:37
+8:02</t>
+        </is>
+      </c>
+      <c r="V73" s="1" t="inlineStr">
+        <is>
+          <t>5:40
+CH2004
+13:40
+8:00</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="Y73" s="1" t="inlineStr">
+        <is>
+          <t>6:41
+CG5901
+14:52
+8:11</t>
+        </is>
+      </c>
+      <c r="Z73" s="1" t="inlineStr">
+        <is>
+          <t>5:50
+CF0007
+13:50
+8:00</t>
+        </is>
+      </c>
+      <c r="AA73" s="1" t="inlineStr">
+        <is>
+          <t>5:44
+CH0006
+13:59
+8:15</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="AD73" s="1" t="inlineStr">
+        <is>
+          <t>10:20
+CF1019
+18:20
+8:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>A026935</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>林鈺嵐</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="inlineStr">
+        <is>
+          <t>15:14
+CF0524
+24:31
+9:17</t>
+        </is>
+      </c>
+      <c r="D74" s="1" t="inlineStr">
+        <is>
+          <t>12:13
+CH1501
+20:14
+8:01</t>
+        </is>
+      </c>
+      <c r="E74" s="1" t="inlineStr">
+        <is>
+          <t>15:20
+CG0523
+24:31
+9:11</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="H74" s="1" t="inlineStr">
+        <is>
+          <t>16:31
+CH1526
+24:31
+8:00</t>
+        </is>
+      </c>
+      <c r="I74" s="1" t="inlineStr">
+        <is>
+          <t>16:31
+DO2W
+CF3523
+24:31
+8:00</t>
+        </is>
+      </c>
+      <c r="J74" s="1" t="inlineStr">
+        <is>
+          <t>15:27
+CF5902
+23:27
+8:00</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="L74" s="1" t="inlineStr">
+        <is>
+          <t>12:14
+CH0501
+20:14
+8:00</t>
+        </is>
+      </c>
+      <c r="M74" s="1" t="inlineStr">
+        <is>
+          <t>12:37
+CF0503
+20:37
+8:00</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="O74" s="1" t="inlineStr">
+        <is>
+          <t>12:25
+CF0513
+22:14
+9:49</t>
+        </is>
+      </c>
+      <c r="P74" s="1" t="inlineStr">
+        <is>
+          <t>12:40
+CG1504
+20:40
+8:00</t>
+        </is>
+      </c>
+      <c r="Q74" s="1" t="inlineStr">
+        <is>
+          <t>10:45
+CH0021
+18:45
+8:00</t>
+        </is>
+      </c>
+      <c r="R74" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+LUTS
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T74" s="1" t="inlineStr">
+        <is>
+          <t>5:15
+CF0001
+13:15
+8:00</t>
+        </is>
+      </c>
+      <c r="U74" s="1" t="inlineStr">
+        <is>
+          <t>6:41
+CG0011
+14:59
+8:18</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="W74" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+PAY
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="Y74" s="1" t="inlineStr">
+        <is>
+          <t>9:37
+CG5903
+18:08
+8:31</t>
+        </is>
+      </c>
+      <c r="Z74" s="1" t="inlineStr">
+        <is>
+          <t>5:40
+CF0004
+13:56
+8:16</t>
+        </is>
+      </c>
+      <c r="AA74" s="1" t="inlineStr">
+        <is>
+          <t>5:44
+CG0006
+13:59
+8:15</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="AD74" s="1" t="inlineStr">
+        <is>
+          <t>5:35
+CH1003
+13:37
+8:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>A027633</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>陳薇媗</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="inlineStr">
+        <is>
+          <t>14:13
+CF1513
+22:14
+8:01</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="F75" s="1" t="inlineStr">
+        <is>
+          <t>6:31
+CG0011
+14:59
+8:28</t>
+        </is>
+      </c>
+      <c r="G75" s="1" t="inlineStr">
+        <is>
+          <t>6:02
+CH1008
+14:40
+8:38</t>
+        </is>
+      </c>
+      <c r="H75" s="1" t="inlineStr">
+        <is>
+          <t>5:15
+CF1001
+13:15
+8:00</t>
+        </is>
+      </c>
+      <c r="I75" s="1" t="inlineStr">
+        <is>
+          <t>5:35
+DO2W
+CG1003
+13:37
+8:02</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="K75" s="1" t="inlineStr">
+        <is>
+          <t>6:02
+CF2008
+14:02
+8:00</t>
+        </is>
+      </c>
+      <c r="L75" s="1" t="inlineStr">
+        <is>
+          <t>6:41
+CF0011
+14:59
+8:18</t>
+        </is>
+      </c>
+      <c r="M75" s="1" t="inlineStr">
+        <is>
+          <t>5:50
+CH0007
+13:50
+8:00</t>
+        </is>
+      </c>
+      <c r="N75" s="1" t="inlineStr">
+        <is>
+          <t>5:35
+CF0003
+13:37
+8:02</t>
+        </is>
+      </c>
+      <c r="O75" s="1" t="inlineStr">
+        <is>
+          <t>5:40
+CH2004
+13:40
+8:00</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="R75" s="1" t="inlineStr">
+        <is>
+          <t>5:35
+CG1002
+13:45
+8:10</t>
+        </is>
+      </c>
+      <c r="S75" s="1" t="inlineStr">
+        <is>
+          <t>7:30
+TOWN
+16:30
+8:00</t>
+        </is>
+      </c>
+      <c r="T75" s="1" t="inlineStr">
+        <is>
+          <t>5:44
+CH0006
+13:59
+8:15</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="V75" s="1" t="inlineStr">
+        <is>
+          <t>12:25
+CG0513
+22:14
+9:49</t>
+        </is>
+      </c>
+      <c r="W75" s="1" t="inlineStr">
+        <is>
+          <t>12:59
+CH0506
+20:59
+8:00</t>
+        </is>
+      </c>
+      <c r="X75" s="1" t="inlineStr">
+        <is>
+          <t>10:40
+DO2W
+CG0020
+19:14
+8:34</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="Z75" s="1" t="inlineStr">
+        <is>
+          <t>15:20
+CF0523
+24:31
+9:11</t>
+        </is>
+      </c>
+      <c r="AA75" s="1" t="inlineStr">
+        <is>
+          <t>15:20
+CH0523
+24:31
+9:11</t>
+        </is>
+      </c>
+      <c r="AB75" s="1" t="inlineStr">
+        <is>
+          <t>15:40
+CF0522
+24:01
+8:21</t>
+        </is>
+      </c>
+      <c r="AC75" s="1" t="inlineStr">
+        <is>
+          <t>12:08
+CG2501
+20:14
+8:06</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>A027643</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>羅芷葳</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="inlineStr">
+        <is>
+          <t>11:13
+CF0025
+21:04
+9:51</t>
+        </is>
+      </c>
+      <c r="D76" s="1" t="inlineStr">
+        <is>
+          <t>12:37
+CF1503
+20:37
+8:00</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="G76" s="1" t="inlineStr">
+        <is>
+          <t>9:57
+CH1022
+19:14
+9:17</t>
+        </is>
+      </c>
+      <c r="H76" s="1" t="inlineStr">
+        <is>
+          <t>8:33
+CF5903
+17:14
+8:41</t>
+        </is>
+      </c>
+      <c r="I76" s="1" t="inlineStr">
+        <is>
+          <t>7:33
+CG0013
+16:37
+9:04</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="K76" s="1" t="inlineStr">
+        <is>
+          <t>10:52
+CG0022
+19:52
+9:00</t>
+        </is>
+      </c>
+      <c r="L76" s="1" t="inlineStr">
+        <is>
+          <t>12:14
+CF0501
+20:14
+8:00</t>
+        </is>
+      </c>
+      <c r="M76" s="1" t="inlineStr">
+        <is>
+          <t>13:56
+CF0511
+21:56
+8:00</t>
+        </is>
+      </c>
+      <c r="N76" s="1" t="inlineStr">
+        <is>
+          <t>10:56
+CG1022
+19:52
+8:56</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="P76" s="1" t="inlineStr">
+        <is>
+          <t>7:33
+CF0013
+16:37
+9:04</t>
+        </is>
+      </c>
+      <c r="Q76" s="1" t="inlineStr">
+        <is>
+          <t>12:14
+CF3501
+20:14
+8:00</t>
+        </is>
+      </c>
+      <c r="R76" s="1" t="inlineStr">
+        <is>
+          <t>12:37
+CF1503
+20:37
+8:00</t>
+        </is>
+      </c>
+      <c r="S76" s="1" t="inlineStr">
+        <is>
+          <t>12:14
+CG0501
+20:14
+8:00</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="V76" s="1" t="inlineStr">
+        <is>
+          <t>12:04
+CG0507
+21:00
+8:56</t>
+        </is>
+      </c>
+      <c r="W76" s="1" t="inlineStr">
+        <is>
+          <t>13:08
+CH0508
+21:08
+8:00</t>
+        </is>
+      </c>
+      <c r="X76" s="1" t="inlineStr">
+        <is>
+          <t>13:17
+DO2W
+CF0517
+23:03
+9:46</t>
+        </is>
+      </c>
+      <c r="Y76" s="1" t="inlineStr">
+        <is>
+          <t>15:40
+CH0522
+24:01
+8:21</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="AB76" s="1" t="inlineStr">
+        <is>
+          <t>16:31
+CG2525
+24:31
+8:00</t>
+        </is>
+      </c>
+      <c r="AC76" s="1" t="inlineStr">
+        <is>
+          <t>16:13
+CG2523
+24:31
+8:18</t>
+        </is>
+      </c>
+      <c r="AD76" s="1" t="inlineStr">
+        <is>
+          <t>16:28
+CF0526
+24:31
+8:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>A027872</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>陳思穎</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>11:13
+CG0025
+21:04
+9:51</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="E77" s="1" t="inlineStr">
+        <is>
+          <t>13:20
+CG0512
+21:59
+8:39</t>
+        </is>
+      </c>
+      <c r="F77" s="1" t="inlineStr">
+        <is>
+          <t>15:20
+CG0523
+24:31
+9:11</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="H77" s="1" t="inlineStr">
+        <is>
+          <t>16:01
+CF1522
+24:01
+8:00</t>
+        </is>
+      </c>
+      <c r="I77" s="1" t="inlineStr">
+        <is>
+          <t>15:17
+DO2W
+CH5903
+24:28
+9:11</t>
+        </is>
+      </c>
+      <c r="J77" s="1" t="inlineStr">
+        <is>
+          <t>15:17
+CF0524
+24:31
+9:14</t>
+        </is>
+      </c>
+      <c r="K77" s="1" t="inlineStr">
+        <is>
+          <t>15:52
+CF1525
+24:31
+8:39</t>
+        </is>
+      </c>
+      <c r="L77" s="1" t="inlineStr">
+        <is>
+          <t>15:20
+CG0523
+24:31
+9:11</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="O77" s="1" t="inlineStr">
+        <is>
+          <t>12:04
+CH0507
+21:00
+8:56</t>
+        </is>
+      </c>
+      <c r="P77" s="1" t="inlineStr">
+        <is>
+          <t>13:08
+CF0508
+21:08
+8:00</t>
+        </is>
+      </c>
+      <c r="Q77" s="1" t="inlineStr">
+        <is>
+          <t>11:13
+CF0025
+21:04
+9:51</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="S77" s="1" t="inlineStr">
+        <is>
+          <t>15:20
+CF0523
+24:31
+9:11</t>
+        </is>
+      </c>
+      <c r="T77" s="1" t="inlineStr">
+        <is>
+          <t>15:20
+CF0523
+24:31
+9:11</t>
+        </is>
+      </c>
+      <c r="U77" s="1" t="inlineStr">
+        <is>
+          <t>15:20
+CH1523
+24:31
+9:11</t>
+        </is>
+      </c>
+      <c r="V77" s="1" t="inlineStr">
+        <is>
+          <t>15:17
+CG0518
+23:42
+8:25</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X77" s="1" t="inlineStr">
+        <is>
+          <t>13:17
+DO2W
+CH0517
+23:03
+9:46</t>
+        </is>
+      </c>
+      <c r="Y77" s="1" t="inlineStr">
+        <is>
+          <t>15:17
+CG0523
+24:31
+9:14</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="AB77" s="1" t="inlineStr">
+        <is>
+          <t>11:45
+CG1026
+20:14
+8:29</t>
+        </is>
+      </c>
+      <c r="AC77" s="1" t="inlineStr">
+        <is>
+          <t>10:20
+CH0019
+19:14
+8:54</t>
+        </is>
+      </c>
+      <c r="AD77" s="1" t="inlineStr">
+        <is>
+          <t>16:08
+CF0527
+24:08
+8:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>A027873</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>張莘珆</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="inlineStr">
+        <is>
+          <t>16:17
+CF1526
+24:31
+8:14</t>
+        </is>
+      </c>
+      <c r="D78" s="1" t="inlineStr">
+        <is>
+          <t>15:52
+CG1525
+24:31
+8:39</t>
+        </is>
+      </c>
+      <c r="E78" s="1" t="inlineStr">
+        <is>
+          <t>16:20
+CG0525
+24:31
+8:11</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="H78" s="1" t="inlineStr">
+        <is>
+          <t>8:33
+CG5903
+17:14
+8:41</t>
+        </is>
+      </c>
+      <c r="I78" s="1" t="inlineStr">
+        <is>
+          <t>10:20
+DO2W
+CF1019
+18:52
+8:32</t>
+        </is>
+      </c>
+      <c r="J78" s="1" t="inlineStr">
+        <is>
+          <t>10:14
+CH3501
+20:04
+9:50</t>
+        </is>
+      </c>
+      <c r="K78" s="1" t="inlineStr">
+        <is>
+          <t>10:52
+CH0022
+19:52
+9:00</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="N78" s="1" t="inlineStr">
+        <is>
+          <t>5:15
+CH0001
+13:15
+8:00</t>
+        </is>
+      </c>
+      <c r="O78" s="1" t="inlineStr">
+        <is>
+          <t>6:02
+CH3008
+14:02
+8:00</t>
+        </is>
+      </c>
+      <c r="P78" s="1" t="inlineStr">
+        <is>
+          <t>7:33
+CG0013
+16:37
+9:04</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="R78" s="1" t="inlineStr">
+        <is>
+          <t>5:44
+CH0006
+13:59
+8:15</t>
+        </is>
+      </c>
+      <c r="S78" s="1" t="inlineStr">
+        <is>
+          <t>6:02
+CF0008
+14:20
+8:18</t>
+        </is>
+      </c>
+      <c r="T78" s="1" t="inlineStr">
+        <is>
+          <t>5:40
+CG0004
+13:56
+8:16</t>
+        </is>
+      </c>
+      <c r="U78" s="1" t="inlineStr">
+        <is>
+          <t>6:02
+CG1008
+14:40
+8:38</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="W78" s="1" t="inlineStr">
+        <is>
+          <t>5:15
+CF0001
+13:15
+8:00</t>
+        </is>
+      </c>
+      <c r="X78" s="1" t="inlineStr">
+        <is>
+          <t>7:14
+DO2W
+CF5901
+15:14
+8:00</t>
+        </is>
+      </c>
+      <c r="Y78" s="1" t="inlineStr">
+        <is>
+          <t>5:35
+CH1002
+14:00
+8:25</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="AB78" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+OGT2
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="AC78" s="1" t="inlineStr">
+        <is>
+          <t>9:20
+CG0018
+18:45
+9:25</t>
+        </is>
+      </c>
+      <c r="AD78" s="1" t="inlineStr">
+        <is>
+          <t>11:45
+CG0027
+19:45
+8:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>A028065</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>蔡宇翔</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="D79" s="1" t="inlineStr">
+        <is>
+          <t>5:44
+CG0006
+13:59
+8:15</t>
+        </is>
+      </c>
+      <c r="E79" s="1" t="inlineStr">
+        <is>
+          <t>6:02
+CG0008
+14:20
+8:18</t>
+        </is>
+      </c>
+      <c r="F79" s="1" t="inlineStr">
+        <is>
+          <t>6:31
+CF0011
+14:59
+8:28</t>
+        </is>
+      </c>
+      <c r="G79" s="1" t="inlineStr">
+        <is>
+          <t>5:44
+CH1006
+14:59
+9:15</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="I79" s="1" t="inlineStr">
+        <is>
+          <t>16:17
+DO2W
+CF0526
+24:31
+8:14</t>
+        </is>
+      </c>
+      <c r="J79" s="1" t="inlineStr">
+        <is>
+          <t>15:17
+CG0524
+24:31
+9:14</t>
+        </is>
+      </c>
+      <c r="K79" s="1" t="inlineStr">
+        <is>
+          <t>15:20
+CG0523
+24:31
+9:11</t>
+        </is>
+      </c>
+      <c r="L79" s="1" t="inlineStr">
+        <is>
+          <t>16:20
+CF0525
+24:31
+8:11</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="O79" s="1" t="inlineStr">
+        <is>
+          <t>16:01
+CF1522
+24:01
+8:00</t>
+        </is>
+      </c>
+      <c r="P79" s="1" t="inlineStr">
+        <is>
+          <t>16:31
+CH3523
+24:31
+8:00</t>
+        </is>
+      </c>
+      <c r="Q79" s="1" t="inlineStr">
+        <is>
+          <t>15:14
+CH0524
+24:31
+9:17</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="S79" s="1" t="inlineStr">
+        <is>
+          <t>15:40
+CG0522
+24:01
+8:21</t>
+        </is>
+      </c>
+      <c r="T79" s="1" t="inlineStr">
+        <is>
+          <t>13:20
+CF0512
+21:59
+8:39</t>
+        </is>
+      </c>
+      <c r="U79" s="1" t="inlineStr">
+        <is>
+          <t>16:31
+CF2525
+24:31
+8:00</t>
+        </is>
+      </c>
+      <c r="V79" s="1" t="inlineStr">
+        <is>
+          <t>12:40
+CG0504
+20:40
+8:00</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X79" s="1" t="inlineStr">
         <is>
           <t>11:59
 DO2W
@@ -14508,341 +16208,33 @@
 9:41</t>
         </is>
       </c>
-      <c r="Y71" s="1" t="inlineStr">
-        <is>
-          <t>10:17
-CG5904
-19:56
-9:39</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="AB71" s="1" t="inlineStr">
-        <is>
-          <t>6:41
-CF0011
-14:59
-8:18</t>
-        </is>
-      </c>
-      <c r="AC71" s="1" t="inlineStr">
-        <is>
-          <t>5:44
-CF0006
-13:59
-8:15</t>
-        </is>
-      </c>
-      <c r="AD71" s="1" t="inlineStr">
-        <is>
-          <t>6:02
-CF0009
-14:02
-8:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>A026933</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>蕭任求</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>13:56
-CF1518
-23:42
-9:46</t>
-        </is>
-      </c>
-      <c r="D72" s="1" t="inlineStr">
-        <is>
-          <t>15:52
-CF1525
-24:31
-8:39</t>
-        </is>
-      </c>
-      <c r="E72" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="F72" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="I72" s="1" t="inlineStr">
-        <is>
-          <t>16:31
-DO2W
-CH3523
-24:31
-8:00</t>
-        </is>
-      </c>
-      <c r="J72" s="1" t="inlineStr">
-        <is>
-          <t>13:56
-CG1518
-23:42
-9:46</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="L72" s="1" t="inlineStr">
-        <is>
-          <t>15:20
-CH0523
-24:31
-9:11</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="N72" s="1" t="inlineStr">
-        <is>
-          <t>12:37
-CG0503
-20:37
-8:00</t>
-        </is>
-      </c>
-      <c r="O72" s="1" t="inlineStr">
-        <is>
-          <t>12:40
-CG0504
-20:40
-8:00</t>
-        </is>
-      </c>
-      <c r="P72" s="1" t="inlineStr">
-        <is>
-          <t>12:59
-CG0506
-20:59
-8:00</t>
-        </is>
-      </c>
-      <c r="Q72" s="1" t="inlineStr">
-        <is>
-          <t>15:14
-CG0524
-24:31
-9:17</t>
-        </is>
-      </c>
-      <c r="R72" s="1" t="inlineStr">
-        <is>
-          <t>15:20
-CG0523
-24:31
-9:11</t>
-        </is>
-      </c>
-      <c r="S72" s="1" t="inlineStr">
-        <is>
-          <t>13:20
-CH0512
-21:59
-8:39</t>
-        </is>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="V72" s="1" t="inlineStr">
-        <is>
-          <t>5:35
-CF1002
-13:45
-8:10</t>
-        </is>
-      </c>
-      <c r="W72" s="1" t="inlineStr">
-        <is>
-          <t>6:02
-CH0009
-14:02
-8:00</t>
-        </is>
-      </c>
-      <c r="X72" s="1" t="inlineStr">
-        <is>
-          <t>5:35
-DO2W
-CG2003
-13:40
-8:05</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="Z72" s="1" t="inlineStr">
-        <is>
-          <t>5:35
-CF0002
-14:40
-9:05</t>
-        </is>
-      </c>
-      <c r="AA72" s="1" t="inlineStr">
-        <is>
-          <t>6:41
-CG0011
-14:59
-8:18</t>
-        </is>
-      </c>
-      <c r="AB72" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-OGT2
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AC72" s="1" t="inlineStr">
-        <is>
-          <t>10:20
-CG0019
-19:14
-8:54</t>
-        </is>
-      </c>
-      <c r="AD72" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>A026934</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>張雁婷</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="E73" s="1" t="inlineStr">
-        <is>
-          <t>12:37
-CG0503
-20:37
-8:00</t>
-        </is>
-      </c>
-      <c r="F73" s="1" t="inlineStr">
-        <is>
-          <t>13:20
-CF0512
-21:59
-8:39</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="I73" s="1" t="inlineStr">
-        <is>
-          <t>16:08
-DO2W
-CG0527
-24:08
-8:00</t>
-        </is>
-      </c>
-      <c r="J73" s="1" t="inlineStr">
-        <is>
-          <t>14:13
-CH1513
-22:14
-8:01</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="M73" s="1" t="inlineStr">
+      <c r="Y79" s="1" t="inlineStr">
+        <is>
+          <t>11:42
+CH0026
+19:42
+8:00</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="AB79" s="1" t="inlineStr">
+        <is>
+          <t>7:42
+CG0014
+15:42
+8:00</t>
+        </is>
+      </c>
+      <c r="AC79" s="1" t="inlineStr">
         <is>
           <t>6:41
 CH0011
@@ -14850,619 +16242,40 @@
 8:18</t>
         </is>
       </c>
-      <c r="N73" s="1" t="inlineStr">
+      <c r="AD79" s="1" t="inlineStr">
         <is>
           <t>6:02
-CH1008
-14:40
-8:38</t>
-        </is>
-      </c>
-      <c r="O73" s="1" t="inlineStr">
-        <is>
-          <t>5:15
-CF1001
-13:15
-8:00</t>
-        </is>
-      </c>
-      <c r="P73" s="1" t="inlineStr">
-        <is>
-          <t>5:35
-CG1003
-13:37
-8:02</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="R73" s="1" t="inlineStr">
-        <is>
-          <t>6:02
-CF2008
+CH0009
 14:02
 8:00</t>
         </is>
       </c>
-      <c r="S73" s="1" t="inlineStr">
-        <is>
-          <t>6:41
-CH0011
-14:59
-8:18</t>
-        </is>
-      </c>
-      <c r="T73" s="1" t="inlineStr">
-        <is>
-          <t>5:44
-CF0006
-13:59
-8:15</t>
-        </is>
-      </c>
-      <c r="U73" s="1" t="inlineStr">
-        <is>
-          <t>5:35
-CF0003
-13:37
-8:02</t>
-        </is>
-      </c>
-      <c r="V73" s="1" t="inlineStr">
-        <is>
-          <t>5:40
-CH2004
-13:40
-8:00</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="Y73" s="1" t="inlineStr">
-        <is>
-          <t>6:41
-CG5901
-14:52
-8:11</t>
-        </is>
-      </c>
-      <c r="Z73" s="1" t="inlineStr">
-        <is>
-          <t>5:50
-CF0007
-13:50
-8:00</t>
-        </is>
-      </c>
-      <c r="AA73" s="1" t="inlineStr">
-        <is>
-          <t>5:44
-CH0006
-13:59
-8:15</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="AD73" s="1" t="inlineStr">
-        <is>
-          <t>10:20
-CF1019
-18:20
-8:00</t>
-        </is>
-      </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>A026935</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>林鈺嵐</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>15:14
-CF0524
-24:31
-9:17</t>
-        </is>
-      </c>
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t>15:40
-CG0522
-24:01
-8:21</t>
-        </is>
-      </c>
-      <c r="E74" s="1" t="inlineStr">
-        <is>
-          <t>15:20
-CG0523
-24:31
-9:11</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="H74" s="1" t="inlineStr">
-        <is>
-          <t>16:31
-CH1526
-24:31
-8:00</t>
-        </is>
-      </c>
-      <c r="I74" s="1" t="inlineStr">
-        <is>
-          <t>16:31
-DO2W
-CF3523
-24:31
-8:00</t>
-        </is>
-      </c>
-      <c r="J74" s="1" t="inlineStr">
-        <is>
-          <t>15:27
-CF5902
-23:27
-8:00</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="L74" s="1" t="inlineStr">
-        <is>
-          <t>12:14
-CH0501
-20:14
-8:00</t>
-        </is>
-      </c>
-      <c r="M74" s="1" t="inlineStr">
-        <is>
-          <t>12:37
-CF0503
-20:37
-8:00</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="O74" s="1" t="inlineStr">
-        <is>
-          <t>12:25
-CF0513
-22:14
-9:49</t>
-        </is>
-      </c>
-      <c r="P74" s="1" t="inlineStr">
-        <is>
-          <t>12:40
-CG1504
-20:40
-8:00</t>
-        </is>
-      </c>
-      <c r="Q74" s="1" t="inlineStr">
-        <is>
-          <t>10:45
-CH0021
-18:45
-8:00</t>
-        </is>
-      </c>
-      <c r="R74" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUTS
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="T74" s="1" t="inlineStr">
-        <is>
-          <t>5:15
-CF0001
-13:15
-8:00</t>
-        </is>
-      </c>
-      <c r="U74" s="1" t="inlineStr">
-        <is>
-          <t>6:41
-CG0011
-14:59
-8:18</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="W74" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="Y74" s="1" t="inlineStr">
-        <is>
-          <t>9:37
-CG5903
-18:08
-8:31</t>
-        </is>
-      </c>
-      <c r="Z74" s="1" t="inlineStr">
-        <is>
-          <t>5:40
-CF0004
-13:56
-8:16</t>
-        </is>
-      </c>
-      <c r="AA74" s="1" t="inlineStr">
-        <is>
-          <t>5:44
-CG0006
-13:59
-8:15</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="AD74" s="1" t="inlineStr">
-        <is>
-          <t>5:35
-CH1003
-13:37
-8:02</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>A027633</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>陳薇媗</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>14:13
-CF1513
-22:14
-8:01</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="F75" s="1" t="inlineStr">
-        <is>
-          <t>6:31
-CG0011
-14:59
-8:28</t>
-        </is>
-      </c>
-      <c r="G75" s="1" t="inlineStr">
-        <is>
-          <t>6:02
-CH1008
-14:40
-8:38</t>
-        </is>
-      </c>
-      <c r="H75" s="1" t="inlineStr">
-        <is>
-          <t>5:15
-CF1001
-13:15
-8:00</t>
-        </is>
-      </c>
-      <c r="I75" s="1" t="inlineStr">
-        <is>
-          <t>5:35
-DO2W
-CG1003
-13:37
-8:02</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="K75" s="1" t="inlineStr">
-        <is>
-          <t>6:02
-CF2008
-14:02
-8:00</t>
-        </is>
-      </c>
-      <c r="L75" s="1" t="inlineStr">
-        <is>
-          <t>6:41
-CF0011
-14:59
-8:18</t>
-        </is>
-      </c>
-      <c r="M75" s="1" t="inlineStr">
-        <is>
-          <t>5:50
-CH0007
-13:50
-8:00</t>
-        </is>
-      </c>
-      <c r="N75" s="1" t="inlineStr">
-        <is>
-          <t>5:35
-CF0003
-13:37
-8:02</t>
-        </is>
-      </c>
-      <c r="O75" s="1" t="inlineStr">
-        <is>
-          <t>5:40
-CH2004
-13:40
-8:00</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="R75" s="1" t="inlineStr">
-        <is>
-          <t>5:35
-CG1002
-13:45
-8:10</t>
-        </is>
-      </c>
-      <c r="S75" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
-        </is>
-      </c>
-      <c r="T75" s="1" t="inlineStr">
-        <is>
-          <t>5:44
-CH0006
-13:59
-8:15</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="V75" s="1" t="inlineStr">
-        <is>
-          <t>12:25
-CG0513
-22:14
-9:49</t>
-        </is>
-      </c>
-      <c r="W75" s="1" t="inlineStr">
-        <is>
-          <t>12:59
-CH0506
-20:59
-8:00</t>
-        </is>
-      </c>
-      <c r="X75" s="1" t="inlineStr">
-        <is>
-          <t>10:40
-DO2W
-CG0020
-19:14
-8:34</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="Z75" s="1" t="inlineStr">
-        <is>
-          <t>15:20
-CF0523
-24:31
-9:11</t>
-        </is>
-      </c>
-      <c r="AA75" s="1" t="inlineStr">
-        <is>
-          <t>15:20
-CH0523
-24:31
-9:11</t>
-        </is>
-      </c>
-      <c r="AB75" s="1" t="inlineStr">
-        <is>
-          <t>15:40
-CF0522
-24:01
-8:21</t>
-        </is>
-      </c>
-      <c r="AC75" s="1" t="inlineStr">
-        <is>
-          <t>12:08
-CG2501
-20:14
-8:06</t>
-        </is>
-      </c>
-      <c r="AD75" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>A027643</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>羅芷葳</t>
-        </is>
-      </c>
-      <c r="C76" s="1" t="inlineStr">
-        <is>
-          <t>11:13
-CF0025
-21:04
-9:51</t>
-        </is>
-      </c>
-      <c r="D76" s="1" t="inlineStr">
-        <is>
-          <t>12:37
-CF1503
-20:37
-8:00</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="G76" s="1" t="inlineStr">
-        <is>
-          <t>6:02
-CG1008
-14:40
-8:38</t>
-        </is>
-      </c>
-      <c r="H76" s="1" t="inlineStr">
-        <is>
-          <t>6:02
-CG3008
-14:02
-8:00</t>
-        </is>
-      </c>
-      <c r="I76" s="1" t="inlineStr">
-        <is>
-          <t>7:33
-CG0013
-16:37
-9:04</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="K76" s="1" t="inlineStr">
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>A028066</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>馮祥庭</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="inlineStr">
+        <is>
+          <t>11:54
+CF0028
+21:40
+9:46</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="E80" s="1" t="inlineStr">
         <is>
           <t>10:52
 CG0022
@@ -15470,819 +16283,6 @@
 9:00</t>
         </is>
       </c>
-      <c r="L76" s="1" t="inlineStr">
-        <is>
-          <t>12:14
-CF0501
-20:14
-8:00</t>
-        </is>
-      </c>
-      <c r="M76" s="1" t="inlineStr">
-        <is>
-          <t>13:56
-CF0511
-21:56
-8:00</t>
-        </is>
-      </c>
-      <c r="N76" s="1" t="inlineStr">
-        <is>
-          <t>11:13
-CG0023
-19:28
-8:15</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="P76" s="1" t="inlineStr">
-        <is>
-          <t>7:33
-CF0013
-16:37
-9:04</t>
-        </is>
-      </c>
-      <c r="Q76" s="1" t="inlineStr">
-        <is>
-          <t>6:02
-CG1009
-14:31
-8:29</t>
-        </is>
-      </c>
-      <c r="R76" s="1" t="inlineStr">
-        <is>
-          <t>12:37
-CF1503
-20:37
-8:00</t>
-        </is>
-      </c>
-      <c r="S76" s="1" t="inlineStr">
-        <is>
-          <t>12:14
-CG0501
-20:14
-8:00</t>
-        </is>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="V76" s="1" t="inlineStr">
-        <is>
-          <t>12:04
-CG0507
-21:00
-8:56</t>
-        </is>
-      </c>
-      <c r="W76" s="1" t="inlineStr">
-        <is>
-          <t>13:08
-CH0508
-21:08
-8:00</t>
-        </is>
-      </c>
-      <c r="X76" s="1" t="inlineStr">
-        <is>
-          <t>13:17
-DO2W
-CF0517
-23:03
-9:46</t>
-        </is>
-      </c>
-      <c r="Y76" s="1" t="inlineStr">
-        <is>
-          <t>15:40
-CH0522
-24:01
-8:21</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="AB76" s="1" t="inlineStr">
-        <is>
-          <t>16:31
-CG2525
-24:31
-8:00</t>
-        </is>
-      </c>
-      <c r="AC76" s="1" t="inlineStr">
-        <is>
-          <t>16:13
-CG2523
-24:31
-8:18</t>
-        </is>
-      </c>
-      <c r="AD76" s="1" t="inlineStr">
-        <is>
-          <t>16:28
-CF0526
-24:31
-8:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>A027872</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>陳思穎</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>11:13
-CG0025
-21:04
-9:51</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="E77" s="1" t="inlineStr">
-        <is>
-          <t>13:20
-CG0512
-21:59
-8:39</t>
-        </is>
-      </c>
-      <c r="F77" s="1" t="inlineStr">
-        <is>
-          <t>15:20
-CG0523
-24:31
-9:11</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="H77" s="1" t="inlineStr">
-        <is>
-          <t>16:01
-CF1522
-24:01
-8:00</t>
-        </is>
-      </c>
-      <c r="I77" s="1" t="inlineStr">
-        <is>
-          <t>15:17
-DO2W
-CH5903
-24:28
-9:11</t>
-        </is>
-      </c>
-      <c r="J77" s="1" t="inlineStr">
-        <is>
-          <t>15:17
-CF0524
-24:31
-9:14</t>
-        </is>
-      </c>
-      <c r="K77" s="1" t="inlineStr">
-        <is>
-          <t>15:52
-CF1525
-24:31
-8:39</t>
-        </is>
-      </c>
-      <c r="L77" s="1" t="inlineStr">
-        <is>
-          <t>15:20
-CG0523
-24:31
-9:11</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="O77" s="1" t="inlineStr">
-        <is>
-          <t>12:04
-CH0507
-21:00
-8:56</t>
-        </is>
-      </c>
-      <c r="P77" s="1" t="inlineStr">
-        <is>
-          <t>13:08
-CF0508
-21:08
-8:00</t>
-        </is>
-      </c>
-      <c r="Q77" s="1" t="inlineStr">
-        <is>
-          <t>11:13
-CF0025
-21:04
-9:51</t>
-        </is>
-      </c>
-      <c r="R77" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="S77" s="1" t="inlineStr">
-        <is>
-          <t>15:40
-CH0522
-24:01
-8:21</t>
-        </is>
-      </c>
-      <c r="T77" s="1" t="inlineStr">
-        <is>
-          <t>15:20
-CF0523
-24:31
-9:11</t>
-        </is>
-      </c>
-      <c r="U77" s="1" t="inlineStr">
-        <is>
-          <t>15:20
-CH1523
-24:31
-9:11</t>
-        </is>
-      </c>
-      <c r="V77" s="1" t="inlineStr">
-        <is>
-          <t>15:17
-CG0518
-23:42
-8:25</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="X77" s="1" t="inlineStr">
-        <is>
-          <t>13:17
-DO2W
-CH0517
-23:03
-9:46</t>
-        </is>
-      </c>
-      <c r="Y77" s="1" t="inlineStr">
-        <is>
-          <t>15:17
-CG0523
-24:31
-9:14</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="AB77" s="1" t="inlineStr">
-        <is>
-          <t>11:45
-CG1026
-20:14
-8:29</t>
-        </is>
-      </c>
-      <c r="AC77" s="1" t="inlineStr">
-        <is>
-          <t>10:20
-CH0019
-19:14
-8:54</t>
-        </is>
-      </c>
-      <c r="AD77" s="1" t="inlineStr">
-        <is>
-          <t>13:08
-CG0508
-21:08
-8:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>A027873</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>張莘珆</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>16:17
-CF1526
-24:31
-8:14</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>15:52
-CG1525
-24:31
-8:39</t>
-        </is>
-      </c>
-      <c r="E78" s="1" t="inlineStr">
-        <is>
-          <t>16:20
-CG0525
-24:31
-8:11</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="H78" s="1" t="inlineStr">
-        <is>
-          <t>8:33
-CG5903
-17:14
-8:41</t>
-        </is>
-      </c>
-      <c r="I78" s="1" t="inlineStr">
-        <is>
-          <t>10:20
-DO2W
-CF1019
-18:52
-8:32</t>
-        </is>
-      </c>
-      <c r="J78" s="1" t="inlineStr">
-        <is>
-          <t>10:14
-CH3501
-20:04
-9:50</t>
-        </is>
-      </c>
-      <c r="K78" s="1" t="inlineStr">
-        <is>
-          <t>10:52
-CH0022
-19:52
-9:00</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="N78" s="1" t="inlineStr">
-        <is>
-          <t>5:15
-CH0001
-13:15
-8:00</t>
-        </is>
-      </c>
-      <c r="O78" s="1" t="inlineStr">
-        <is>
-          <t>6:02
-CH3008
-14:02
-8:00</t>
-        </is>
-      </c>
-      <c r="P78" s="1" t="inlineStr">
-        <is>
-          <t>7:33
-CG0013
-16:37
-9:04</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="R78" s="1" t="inlineStr">
-        <is>
-          <t>5:44
-CH0006
-13:59
-8:15</t>
-        </is>
-      </c>
-      <c r="S78" s="1" t="inlineStr">
-        <is>
-          <t>6:02
-CF0008
-14:20
-8:18</t>
-        </is>
-      </c>
-      <c r="T78" s="1" t="inlineStr">
-        <is>
-          <t>5:40
-CG0004
-13:56
-8:16</t>
-        </is>
-      </c>
-      <c r="U78" s="1" t="inlineStr">
-        <is>
-          <t>6:02
-CG1008
-14:40
-8:38</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="W78" s="1" t="inlineStr">
-        <is>
-          <t>5:15
-CF0001
-13:15
-8:00</t>
-        </is>
-      </c>
-      <c r="X78" s="1" t="inlineStr">
-        <is>
-          <t>7:14
-DO2W
-CF5901
-15:14
-8:00</t>
-        </is>
-      </c>
-      <c r="Y78" s="1" t="inlineStr">
-        <is>
-          <t>5:35
-CH1002
-14:00
-8:25</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="AB78" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-OGT2
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AC78" s="1" t="inlineStr">
-        <is>
-          <t>9:20
-CG0018
-18:45
-9:25</t>
-        </is>
-      </c>
-      <c r="AD78" s="1" t="inlineStr">
-        <is>
-          <t>11:45
-CG0027
-19:45
-8:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>A028065</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>蔡宇翔</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>5:44
-CG0006
-13:59
-8:15</t>
-        </is>
-      </c>
-      <c r="E79" s="1" t="inlineStr">
-        <is>
-          <t>6:02
-CG0008
-14:20
-8:18</t>
-        </is>
-      </c>
-      <c r="F79" s="1" t="inlineStr">
-        <is>
-          <t>6:31
-CF0011
-14:59
-8:28</t>
-        </is>
-      </c>
-      <c r="G79" s="1" t="inlineStr">
-        <is>
-          <t>5:44
-CH1006
-14:59
-9:15</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="I79" s="1" t="inlineStr">
-        <is>
-          <t>16:17
-DO2W
-CF0526
-24:31
-8:14</t>
-        </is>
-      </c>
-      <c r="J79" s="1" t="inlineStr">
-        <is>
-          <t>15:17
-CG0524
-24:31
-9:14</t>
-        </is>
-      </c>
-      <c r="K79" s="1" t="inlineStr">
-        <is>
-          <t>15:20
-CG0523
-24:31
-9:11</t>
-        </is>
-      </c>
-      <c r="L79" s="1" t="inlineStr">
-        <is>
-          <t>16:20
-CF0525
-24:31
-8:11</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="O79" s="1" t="inlineStr">
-        <is>
-          <t>16:01
-CF1522
-24:01
-8:00</t>
-        </is>
-      </c>
-      <c r="P79" s="1" t="inlineStr">
-        <is>
-          <t>16:31
-CH3523
-24:31
-8:00</t>
-        </is>
-      </c>
-      <c r="Q79" s="1" t="inlineStr">
-        <is>
-          <t>15:14
-CH0524
-24:31
-9:17</t>
-        </is>
-      </c>
-      <c r="R79" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="S79" s="1" t="inlineStr">
-        <is>
-          <t>15:40
-CG0522
-24:01
-8:21</t>
-        </is>
-      </c>
-      <c r="T79" s="1" t="inlineStr">
-        <is>
-          <t>13:20
-CF0512
-21:59
-8:39</t>
-        </is>
-      </c>
-      <c r="U79" s="1" t="inlineStr">
-        <is>
-          <t>15:40
-CG0522
-24:01
-8:21</t>
-        </is>
-      </c>
-      <c r="V79" s="1" t="inlineStr">
-        <is>
-          <t>12:40
-CG0504
-20:40
-8:00</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="X79" s="1" t="inlineStr">
-        <is>
-          <t>11:18
-DO2W
-CF0025
-21:14
-9:56</t>
-        </is>
-      </c>
-      <c r="Y79" s="1" t="inlineStr">
-        <is>
-          <t>11:42
-CH0026
-19:42
-8:00</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="AB79" s="1" t="inlineStr">
-        <is>
-          <t>7:42
-CG0014
-15:42
-8:00</t>
-        </is>
-      </c>
-      <c r="AC79" s="1" t="inlineStr">
-        <is>
-          <t>6:41
-CH0011
-14:59
-8:18</t>
-        </is>
-      </c>
-      <c r="AD79" s="1" t="inlineStr">
-        <is>
-          <t>6:02
-CH0009
-14:02
-8:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>A028066</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>馮祥庭</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>11:54
-CF0028
-21:40
-9:46</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="E80" s="1" t="inlineStr">
-        <is>
-          <t>10:52
-CG0022
-19:52
-9:00</t>
-        </is>
-      </c>
       <c r="F80" s="1" t="inlineStr">
         <is>
           <t>8:13
@@ -16293,10 +16293,10 @@
       </c>
       <c r="G80" s="1" t="inlineStr">
         <is>
-          <t>12:25
-CG5901
-22:14
-9:49</t>
+          <t>15:17
+CG5902
+23:42
+8:25</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -16349,17 +16349,17 @@
       </c>
       <c r="O80" s="1" t="inlineStr">
         <is>
-          <t>5:44
-CG0006
-13:59
-8:15</t>
+          <t>13:08
+CF0509
+21:14
+8:06</t>
         </is>
       </c>
       <c r="P80" s="1" t="inlineStr">
         <is>
-          <t>5:15
-CH0001
-13:15
+          <t>10:20
+CF1019
+18:20
 8:00</t>
         </is>
       </c>
@@ -16571,9 +16571,9 @@
       </c>
       <c r="P81" s="1" t="inlineStr">
         <is>
-          <t>6:02
-CG0009
-14:02
+          <t>9:17
+CH0017
+17:17
 8:00</t>
         </is>
       </c>
@@ -16634,17 +16634,17 @@
       </c>
       <c r="Y81" s="1" t="inlineStr">
         <is>
-          <t>5:35
-CF1002
-14:00
-8:25</t>
+          <t>12:45
+CH1501
+20:45
+8:00</t>
         </is>
       </c>
       <c r="Z81" s="1" t="inlineStr">
         <is>
-          <t>5:15
-CF0001
-13:15
+          <t>12:37
+CH0503
+20:37
 8:00</t>
         </is>
       </c>
@@ -16974,10 +16974,10 @@
       </c>
       <c r="M83" s="1" t="inlineStr">
         <is>
-          <t>12:14
-CG0501
-20:14
-8:00</t>
+          <t>13:20
+CH0512
+21:59
+8:39</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
